--- a/GourmetProject/GameConfig/Datas/reward_curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_curve.xlsx
@@ -497,67 +497,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>曲线ID</t>
+          <t>隐藏分曲线ID。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Base/TargetScore/Dish/PassiveItem/ActiveItem/Fragment</t>
+          <t>曲线用途：Base/TargetScore/Dish/PassiveItem/ActiveItem/Fragment。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>固定值</t>
+          <t>基础值。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>基础隐藏分倍率</t>
+          <t>基础倍率。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>每周加成</t>
+          <t>每周递增值。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>每天加成</t>
+          <t>每推进一天递增值。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>每行动步加成</t>
+          <t>每执行一次行动递增值。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>普通行动加成</t>
+          <t>普通美食难度加成。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>困难行动加成</t>
+          <t>困难美食难度加成。</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Boss行动加成</t>
+          <t>Boss难度加成。</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>道具隐藏分加成倍率</t>
+          <t>道具隐藏分派生倍率。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>取整粒度</t>
+          <t>向上取整粒度。</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>最小值</t>
+          <t>最小值。</t>
         </is>
       </c>
     </row>
@@ -634,6 +634,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>hidden_base</t>
@@ -679,6 +680,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>hidden_target_score</t>
@@ -724,6 +726,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>hidden_dish</t>
@@ -769,6 +772,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>hidden_passive_item</t>
@@ -814,6 +818,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>hidden_active_item</t>
@@ -859,6 +864,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>hidden_fragment</t>
@@ -997,67 +1003,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>曲线ID</t>
+          <t>金币奖励曲线ID。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>金币下限基础值</t>
+          <t>金币下限基础值。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金币上限基础值</t>
+          <t>金币上限基础值。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>下限每周加成</t>
+          <t>金币下限每周递增值。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>上限每周加成</t>
+          <t>金币上限每周递增值。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>下限每天加成</t>
+          <t>金币下限每行动轴天数递增值。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>上限每天加成</t>
+          <t>金币上限每行动轴天数递增值。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>普通下限加成</t>
+          <t>普通难度金币下限加成。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>普通上限加成</t>
+          <t>普通难度金币上限加成。</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>困难下限加成</t>
+          <t>困难难度金币下限加成。</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>困难上限加成</t>
+          <t>困难难度金币上限加成。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Boss下限加成</t>
+          <t>Boss难度金币下限加成。</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Boss上限加成</t>
+          <t>Boss难度金币上限加成。</t>
         </is>
       </c>
     </row>
@@ -1134,6 +1140,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>gold_normal</t>
@@ -1177,6 +1184,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>gold_hard</t>
@@ -1220,6 +1228,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>gold_boss</t>
@@ -1263,6 +1272,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>gold_fragment_convert</t>

--- a/GourmetProject/GameConfig/Datas/reward_curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_curve.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,55 +435,80 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>segmentPriority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>minWeek</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>maxWeek</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>minRunStep</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>maxRunStep</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>baseValue</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>baseMultiplier</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>perWeek</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>perDay</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>perStep</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>normalBonus</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>hardBonus</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>bossBonus</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>itemBonusMultiplier</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>roundTo</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>minValue</t>
         </is>
@@ -507,55 +532,80 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>分段优先级，数值越大越优先。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>适用最小周数；&lt;=0 表示不限。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>适用最大周数；&lt;=0 表示不限。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>适用最小整局行动序号；&lt;=0 表示不限。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>适用最大整局行动序号；&lt;=0 表示不限。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>基础值。</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>基础倍率。</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>每周递增值。</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>每推进一天递增值。</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>每执行一次行动递增值。</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>普通美食难度加成。</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>困难美食难度加成。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Boss难度加成。</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>道具隐藏分派生倍率。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>向上取整粒度。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>最小值。</t>
         </is>
@@ -584,50 +634,75 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -637,7 +712,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hidden_base</t>
+          <t>hidden_base_early</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -646,36 +721,51 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="P4" t="n">
         <v>16</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,111 +773,141 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hidden_target_score</t>
+          <t>hidden_base_late</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TargetScore</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>30</v>
+      <c r="P5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hidden_dish</t>
+          <t>hidden_target_score_early</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>TargetScore</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>30</v>
+      </c>
+      <c r="P6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hidden_passive_item</t>
+          <t>hidden_target_score_late</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PassiveItem</t>
+          <t>TargetScore</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -799,41 +919,56 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>40</v>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hidden_active_item</t>
+          <t>hidden_dish</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ActiveItem</t>
+          <t>Dish</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -848,18 +983,33 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,45 +1017,182 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
+          <t>hidden_passive_item</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PassiveItem</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hidden_active_item</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ActiveItem</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>hidden_fragment</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Fragment</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="P11" t="n">
         <v>12</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/reward_curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_curve.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,30 +485,15 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>normalBonus</t>
+          <t>itemBonusMultiplier</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>hardBonus</t>
+          <t>roundTo</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>bossBonus</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>itemBonusMultiplier</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>roundTo</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>minValue</t>
         </is>
@@ -582,30 +567,15 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>普通美食难度加成。</t>
+          <t>道具隐藏分派生倍率。</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>困难美食难度加成。</t>
+          <t>向上取整粒度。</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
-        <is>
-          <t>Boss难度加成。</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>道具隐藏分派生倍率。</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>向上取整粒度。</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
         <is>
           <t>最小值。</t>
         </is>
@@ -679,37 +649,21 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>hidden_base_early</t>
@@ -751,26 +705,16 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>hidden_base_late</t>
@@ -812,26 +756,16 @@
         <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>hidden_target_score_early</t>
@@ -876,23 +810,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
         <v>30</v>
       </c>
-      <c r="P6" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>hidden_target_score_late</t>
@@ -937,23 +861,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
         <v>40</v>
       </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>hidden_dish</t>
@@ -998,23 +912,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>hidden_passive_item</t>
@@ -1059,23 +963,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>hidden_active_item</t>
@@ -1120,23 +1014,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>hidden_fragment</t>
@@ -1181,18 +1065,9 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1207,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,36 +1126,6 @@
           <t>maxPerDay</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>normalMinBonus</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>normalMaxBonus</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>hardMinBonus</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>hardMaxBonus</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>bossMinBonus</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>bossMaxBonus</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1323,36 +1168,6 @@
           <t>金币上限每行动轴天数递增值。</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>普通难度金币下限加成。</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>普通难度金币上限加成。</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>困难难度金币下限加成。</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>困难难度金币上限加成。</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Boss难度金币下限加成。</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Boss难度金币上限加成。</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1395,39 +1210,8 @@
           <t>float</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>gold_normal</t>
@@ -1451,27 +1235,8 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" t="n">
-        <v>16</v>
-      </c>
-      <c r="M4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N4" t="n">
-        <v>45</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>gold_hard</t>
@@ -1495,27 +1260,8 @@
       <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L5" t="n">
-        <v>24</v>
-      </c>
-      <c r="M5" t="n">
-        <v>36</v>
-      </c>
-      <c r="N5" t="n">
-        <v>55</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>gold_boss</t>
@@ -1539,27 +1285,8 @@
       <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>45</v>
-      </c>
-      <c r="N6" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>gold_fragment_convert</t>
@@ -1582,24 +1309,6 @@
       </c>
       <c r="H7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" t="n">
-        <v>20</v>
-      </c>
-      <c r="M7" t="n">
-        <v>35</v>
-      </c>
-      <c r="N7" t="n">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/reward_curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_curve.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,11 @@
           <t>maxPerDay</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fluctuationPct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1140,32 +1145,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>金币下限基础值。</t>
+          <t>金币奖励隐藏分下限基础值。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金币上限基础值。</t>
+          <t>金币奖励隐藏分上限基础值。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>金币下限每周递增值。</t>
+          <t>下限每周递增值。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>金币上限每周递增值。</t>
+          <t>上限每周递增值。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>金币下限每行动轴天数递增值。</t>
+          <t>下限每行动轴天数递增值。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>金币上限每行动轴天数递增值。</t>
+          <t>上限每行动轴天数递增值。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>上下浮动比例，例如 0.2 表示下限*0.8、上限*1.2。</t>
         </is>
       </c>
     </row>
@@ -1210,6 +1220,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -1217,23 +1232,26 @@
           <t>gold_normal</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>18</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>30</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>6</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.5</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -1242,23 +1260,26 @@
           <t>gold_hard</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>26</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>44</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.5</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -1267,23 +1288,26 @@
           <t>gold_boss</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>60</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>95</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>12</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>2</v>
+      </c>
+      <c r="I6">
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -1292,23 +1316,26 @@
           <t>gold_fragment_convert</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>22</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>42</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>7</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.5</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/reward_curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_curve.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -102,19 +102,19 @@
     <t>目标分 = exp(k0 + kBase*基础分 + kWeek*周数 + kDay*当周过去天数)</t>
   </si>
   <si>
-    <t>hidden_target_score_1</t>
+    <t>target_score_1</t>
   </si>
   <si>
     <t>TargetScore</t>
   </si>
   <si>
-    <t>hidden_target_score_2</t>
-  </si>
-  <si>
-    <t>hidden_target_score_3</t>
-  </si>
-  <si>
-    <t>hidden_target_score_4</t>
+    <t>target_score_2</t>
+  </si>
+  <si>
+    <t>target_score_3</t>
+  </si>
+  <si>
+    <t>target_score_4</t>
   </si>
   <si>
     <t>hidden_dish</t>
@@ -129,12 +129,6 @@
     <t>PassiveItem</t>
   </si>
   <si>
-    <t>hidden_active_item</t>
-  </si>
-  <si>
-    <t>ActiveItem</t>
-  </si>
-  <si>
     <t>hidden_fragment</t>
   </si>
   <si>
@@ -186,16 +180,7 @@
     <t>上下浮动比例，例如 0.2 表示下限*0.8、上限*1.2。</t>
   </si>
   <si>
-    <t>gold_normal</t>
-  </si>
-  <si>
-    <t>gold_hard</t>
-  </si>
-  <si>
-    <t>gold_boss</t>
-  </si>
-  <si>
-    <t>gold_fragment_convert</t>
+    <t>gold_default</t>
   </si>
 </sst>
 </file>
@@ -3025,7 +3010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -3147,7 +3132,6 @@
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1"/>
       <c r="M3" s="2" t="s">
         <v>27</v>
       </c>
@@ -3346,7 +3330,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -3364,35 +3348,6 @@
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
         <v>1</v>
       </c>
     </row>
@@ -3405,8 +3360,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="20.3846153846154" customWidth="1"/>
+    <col min="3" max="4" width="32.1538461538462" customWidth="1"/>
+    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="7" max="8" width="29.6923076923077" customWidth="1"/>
+    <col min="9" max="9" width="53.3846153846154" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
@@ -3416,25 +3378,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>45</v>
-      </c>
-      <c r="H1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3442,28 +3404,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>51</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>52</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3497,7 +3459,7 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>18</v>
@@ -3518,84 +3480,6 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5">
-        <v>26</v>
-      </c>
-      <c r="D5">
-        <v>44</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>0.5</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6">
-        <v>60</v>
-      </c>
-      <c r="D6">
-        <v>95</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
         <v>0.2</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/reward_curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_curve.xlsx
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -3301,13 +3301,13 @@
         <v>36</v>
       </c>
       <c r="E9" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -3330,13 +3330,13 @@
         <v>38</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
